--- a/data/family_typing_data.xlsx
+++ b/data/family_typing_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wahealthdept-my.sharepoint.com/personal/he144508_health_wa_gov_au/Documents/apps_and_pipelines/HLA_Extended_Haplotypes/HLAhaploTools/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFD8EC02-9AAF-4A80-B149-4B47DA9C6677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{BFD8EC02-9AAF-4A80-B149-4B47DA9C6677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20049102-6D22-40AA-BA7D-E3F50CA6EFCD}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{11F302D0-E60C-42AB-8D5C-AFDE08D6379E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{11F302D0-E60C-42AB-8D5C-AFDE08D6379E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -819,12 +819,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D73C4A4-9A54-490B-BC29-DF6A4F49C745}">
   <dimension ref="A1:AL15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="20" max="20" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -940,7 +941,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>132</v>
       </c>
@@ -1056,7 +1057,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>132</v>
       </c>
@@ -1172,7 +1173,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>132</v>
       </c>
@@ -1288,7 +1289,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>132</v>
       </c>
@@ -1404,7 +1405,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>132</v>
       </c>
@@ -1520,7 +1521,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>133</v>
       </c>
@@ -1636,7 +1637,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>133</v>
       </c>
@@ -1752,7 +1753,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>133</v>
       </c>
@@ -1868,7 +1869,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -1984,7 +1985,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>133</v>
       </c>
@@ -2100,7 +2101,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>134</v>
       </c>
@@ -2216,7 +2217,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>134</v>
       </c>
@@ -2332,7 +2333,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>134</v>
       </c>
@@ -2448,7 +2449,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>134</v>
       </c>
